--- a/artfynd/A 46272-2020 artfynd.xlsx
+++ b/artfynd/A 46272-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46272-2020 artfynd.xlsx
+++ b/artfynd/A 46272-2020 artfynd.xlsx
@@ -3425,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119796327</v>
+        <v>119796326</v>
       </c>
       <c r="B28" t="n">
-        <v>91884</v>
+        <v>91826</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3441,21 +3441,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>694022</v>
+        <v>694055</v>
       </c>
       <c r="R28" t="n">
-        <v>7318134</v>
+        <v>7318187</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119796326</v>
+        <v>119796327</v>
       </c>
       <c r="B29" t="n">
-        <v>91826</v>
+        <v>91884</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3552,21 +3552,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>694055</v>
+        <v>694022</v>
       </c>
       <c r="R29" t="n">
-        <v>7318187</v>
+        <v>7318134</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 46272-2020 artfynd.xlsx
+++ b/artfynd/A 46272-2020 artfynd.xlsx
@@ -3425,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119796326</v>
+        <v>119796327</v>
       </c>
       <c r="B28" t="n">
-        <v>91826</v>
+        <v>91884</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3441,21 +3441,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>694055</v>
+        <v>694022</v>
       </c>
       <c r="R28" t="n">
-        <v>7318187</v>
+        <v>7318134</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119796327</v>
+        <v>119796326</v>
       </c>
       <c r="B29" t="n">
-        <v>91884</v>
+        <v>91826</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3552,21 +3552,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>694022</v>
+        <v>694055</v>
       </c>
       <c r="R29" t="n">
-        <v>7318134</v>
+        <v>7318187</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 46272-2020 artfynd.xlsx
+++ b/artfynd/A 46272-2020 artfynd.xlsx
@@ -3428,7 +3428,7 @@
         <v>119796327</v>
       </c>
       <c r="B28" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>119796326</v>
       </c>
       <c r="B29" t="n">
-        <v>91826</v>
+        <v>91844</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 46272-2020 artfynd.xlsx
+++ b/artfynd/A 46272-2020 artfynd.xlsx
@@ -3647,7 +3647,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121149730</v>
+        <v>121149731</v>
       </c>
       <c r="B30" t="n">
         <v>91967</v>
@@ -3659,25 +3659,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>694115</v>
+        <v>694020</v>
       </c>
       <c r="R30" t="n">
-        <v>7318146</v>
+        <v>7318165</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121149731</v>
+        <v>121149732</v>
       </c>
       <c r="B31" t="n">
-        <v>91957</v>
+        <v>91977</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3770,25 +3770,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>694020</v>
+        <v>694027</v>
       </c>
       <c r="R31" t="n">
-        <v>7318165</v>
+        <v>7318029</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121149732</v>
+        <v>121149730</v>
       </c>
       <c r="B32" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3913,10 +3913,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>694027</v>
+        <v>694115</v>
       </c>
       <c r="R32" t="n">
-        <v>7318029</v>
+        <v>7318146</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>

--- a/artfynd/A 46272-2020 artfynd.xlsx
+++ b/artfynd/A 46272-2020 artfynd.xlsx
@@ -3650,7 +3650,7 @@
         <v>121149731</v>
       </c>
       <c r="B30" t="n">
-        <v>91967</v>
+        <v>91979</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121149732</v>
+        <v>121149730</v>
       </c>
       <c r="B31" t="n">
-        <v>91977</v>
+        <v>91989</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>694027</v>
+        <v>694115</v>
       </c>
       <c r="R31" t="n">
-        <v>7318029</v>
+        <v>7318146</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121149730</v>
+        <v>121149732</v>
       </c>
       <c r="B32" t="n">
-        <v>91977</v>
+        <v>91989</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3913,10 +3913,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>694115</v>
+        <v>694027</v>
       </c>
       <c r="R32" t="n">
-        <v>7318146</v>
+        <v>7318029</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>

--- a/artfynd/A 46272-2020 artfynd.xlsx
+++ b/artfynd/A 46272-2020 artfynd.xlsx
@@ -3647,10 +3647,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121149731</v>
+        <v>121149730</v>
       </c>
       <c r="B30" t="n">
-        <v>91979</v>
+        <v>91990</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3659,25 +3659,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>694020</v>
+        <v>694115</v>
       </c>
       <c r="R30" t="n">
-        <v>7318165</v>
+        <v>7318146</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121149730</v>
+        <v>121149731</v>
       </c>
       <c r="B31" t="n">
-        <v>91989</v>
+        <v>91980</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3770,25 +3770,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>694115</v>
+        <v>694020</v>
       </c>
       <c r="R31" t="n">
-        <v>7318146</v>
+        <v>7318165</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3872,7 +3872,7 @@
         <v>121149732</v>
       </c>
       <c r="B32" t="n">
-        <v>91989</v>
+        <v>91990</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 46272-2020 artfynd.xlsx
+++ b/artfynd/A 46272-2020 artfynd.xlsx
@@ -3647,10 +3647,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121149730</v>
+        <v>121149731</v>
       </c>
       <c r="B30" t="n">
-        <v>91990</v>
+        <v>91983</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3659,25 +3659,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>694115</v>
+        <v>694020</v>
       </c>
       <c r="R30" t="n">
-        <v>7318146</v>
+        <v>7318165</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3758,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121149731</v>
+        <v>121149732</v>
       </c>
       <c r="B31" t="n">
-        <v>91980</v>
+        <v>91993</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3770,25 +3770,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>694020</v>
+        <v>694027</v>
       </c>
       <c r="R31" t="n">
-        <v>7318165</v>
+        <v>7318029</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3869,10 +3869,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121149732</v>
+        <v>121149730</v>
       </c>
       <c r="B32" t="n">
-        <v>91990</v>
+        <v>91993</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3913,10 +3913,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>694027</v>
+        <v>694115</v>
       </c>
       <c r="R32" t="n">
-        <v>7318029</v>
+        <v>7318146</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>

--- a/artfynd/A 46272-2020 artfynd.xlsx
+++ b/artfynd/A 46272-2020 artfynd.xlsx
@@ -3758,7 +3758,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121149732</v>
+        <v>121149730</v>
       </c>
       <c r="B31" t="n">
         <v>91993</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>694027</v>
+        <v>694115</v>
       </c>
       <c r="R31" t="n">
-        <v>7318029</v>
+        <v>7318146</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121149730</v>
+        <v>121149732</v>
       </c>
       <c r="B32" t="n">
         <v>91993</v>
@@ -3913,10 +3913,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>694115</v>
+        <v>694027</v>
       </c>
       <c r="R32" t="n">
-        <v>7318146</v>
+        <v>7318029</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
